--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.53</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -696,6 +700,88 @@
       </c>
       <c r="T3" t="n">
         <v>32.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>German Bundesliga</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stuttgart x Mgladbach</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mgladbach</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>15651</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T4" t="n">
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.36</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -782,6 +786,92 @@
       </c>
       <c r="T4" t="n">
         <v>34.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>English Sky Bet Championship</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bolton x Middlesbrough</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bolton</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1089</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>40</v>
+      </c>
+      <c r="T5" t="n">
+        <v>38.2</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,88 @@
       </c>
       <c r="T5" t="n">
         <v>38.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG x Remo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>3232</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>32.93</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-23.xlsx
@@ -922,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.31</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
